--- a/artfynd/A 37204-2025 artfynd.xlsx
+++ b/artfynd/A 37204-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112650918</v>
+        <v>112650917</v>
       </c>
       <c r="B2" t="n">
-        <v>95960</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411856</v>
+        <v>411807</v>
       </c>
       <c r="R2" t="n">
-        <v>7023375</v>
+        <v>7023319</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112650917</v>
+        <v>112650918</v>
       </c>
       <c r="B3" t="n">
-        <v>78945</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411807</v>
+        <v>411856</v>
       </c>
       <c r="R3" t="n">
-        <v>7023319</v>
+        <v>7023375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
